--- a/Excel/GiftPackPet.xlsx
+++ b/Excel/GiftPackPet.xlsx
@@ -1218,11 +1218,11 @@
     <col min="16368" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:2">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:7">
       <c r="A1" s="3"/>
       <c r="B1" s="3"/>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:2">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:7">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
     </row>
@@ -1283,7 +1283,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:7">
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="1:7">
       <c r="C6" s="2">
         <v>1</v>
       </c>
@@ -1300,7 +1300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:7">
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="1:7">
       <c r="C7" s="2">
         <v>2</v>
       </c>
@@ -1317,7 +1317,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" customHeight="1" spans="3:7">
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="1:7">
       <c r="C8" s="2">
         <v>3</v>
       </c>
@@ -1334,7 +1334,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" customHeight="1" spans="3:7">
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="1:7">
       <c r="C9" s="2">
         <v>4</v>
       </c>
@@ -1351,7 +1351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:7">
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="1:7">
       <c r="C10" s="2">
         <v>5</v>
       </c>
@@ -1368,7 +1368,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" s="2" customFormat="1" customHeight="1" spans="3:7">
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:7">
       <c r="C11" s="2">
         <v>6</v>
       </c>
@@ -1385,7 +1385,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" s="2" customFormat="1" customHeight="1" spans="3:7">
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="1:7">
       <c r="C12" s="2">
         <v>7</v>
       </c>
@@ -1402,7 +1402,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="3:7">
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:7">
       <c r="C13" s="2">
         <v>8</v>
       </c>
@@ -1419,7 +1419,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" s="2" customFormat="1" customHeight="1" spans="3:7">
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="1:7">
       <c r="C14" s="2">
         <v>9</v>
       </c>
@@ -1437,7 +1437,7 @@
       </c>
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1"/>
-    <row r="16" s="2" customFormat="1" customHeight="1" spans="3:7">
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="1:7">
       <c r="C16" s="2">
         <v>10</v>
       </c>
@@ -2256,19 +2256,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="76" customHeight="1" spans="7:7">
+    <row r="76" customHeight="1" spans="3:7">
       <c r="G76" s="6"/>
     </row>
-    <row r="77" customHeight="1" spans="7:7">
+    <row r="77" customHeight="1" spans="3:7">
       <c r="G77" s="6"/>
     </row>
-    <row r="78" customHeight="1" spans="7:7">
+    <row r="78" customHeight="1" spans="3:7">
       <c r="G78" s="6"/>
     </row>
-    <row r="79" customHeight="1" spans="7:7">
+    <row r="79" customHeight="1" spans="3:7">
       <c r="G79" s="6"/>
     </row>
-    <row r="80" customHeight="1" spans="7:7">
+    <row r="80" customHeight="1" spans="3:7">
       <c r="G80" s="6"/>
     </row>
     <row r="81" customHeight="1" spans="7:7">

--- a/Excel/GiftPackPet.xlsx
+++ b/Excel/GiftPackPet.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="12">
   <si>
     <t>ID</t>
   </si>
@@ -56,178 +56,13 @@
     <t>int[]</t>
   </si>
   <si>
-    <t>橙色战魂40</t>
+    <t>新手宠物</t>
   </si>
   <si>
     <t>7,33,18,2004,2003</t>
   </si>
   <si>
     <t>40,40,40,40,40</t>
-  </si>
-  <si>
-    <t>橙色法魂40</t>
-  </si>
-  <si>
-    <t>7,34,18,2005,2003</t>
-  </si>
-  <si>
-    <t>橙色道魂40</t>
-  </si>
-  <si>
-    <t>7,35,18,2006,2003</t>
-  </si>
-  <si>
-    <t>橙色战魂45</t>
-  </si>
-  <si>
-    <t>45,45,45,45,45</t>
-  </si>
-  <si>
-    <t>橙色法魂45</t>
-  </si>
-  <si>
-    <t>橙色道魂45</t>
-  </si>
-  <si>
-    <t>橙色战魂50</t>
-  </si>
-  <si>
-    <t>50,50,50,50,50</t>
-  </si>
-  <si>
-    <t>橙色法魂50</t>
-  </si>
-  <si>
-    <t>橙色道魂50</t>
-  </si>
-  <si>
-    <t>红色战魂40</t>
-  </si>
-  <si>
-    <t>7,33,18,2004,2003,2001</t>
-  </si>
-  <si>
-    <t>40,40,40,40,40,40</t>
-  </si>
-  <si>
-    <t>红色法魂40</t>
-  </si>
-  <si>
-    <t>7,34,18,2005,2003,2001</t>
-  </si>
-  <si>
-    <t>红色道魂40</t>
-  </si>
-  <si>
-    <t>7,35,18,2006,2003,2001</t>
-  </si>
-  <si>
-    <t>红色战魂45</t>
-  </si>
-  <si>
-    <t>45,45,45,45,45,45</t>
-  </si>
-  <si>
-    <t>红色法魂45</t>
-  </si>
-  <si>
-    <t>红色道魂45</t>
-  </si>
-  <si>
-    <t>金色战魂40</t>
-  </si>
-  <si>
-    <t>7,33,19,2004,2003,32,52</t>
-  </si>
-  <si>
-    <t>40,40,40,40,40,40,40</t>
-  </si>
-  <si>
-    <t>金色法魂40</t>
-  </si>
-  <si>
-    <t>7,34,19,2005,2003,32,52</t>
-  </si>
-  <si>
-    <t>金色道魂40</t>
-  </si>
-  <si>
-    <t>7,35,19,2006,2003,32,52</t>
-  </si>
-  <si>
-    <t>8,33,19,2004,2003,31,52</t>
-  </si>
-  <si>
-    <t>8,34,19,2005,2003,31,52</t>
-  </si>
-  <si>
-    <t>8,35,19,2006,2003,31,52</t>
-  </si>
-  <si>
-    <t>13,33,19,2004,2003,32,52</t>
-  </si>
-  <si>
-    <t>13,34,19,2005,2003,32,52</t>
-  </si>
-  <si>
-    <t>13,35,19,2006,2003,32,52</t>
-  </si>
-  <si>
-    <t>13,33,24,2004,2003,32,53</t>
-  </si>
-  <si>
-    <t>13,34,24,2005,2003,32,53</t>
-  </si>
-  <si>
-    <t>13,35,24,2006,2003,32,53</t>
-  </si>
-  <si>
-    <t>8,33,18,2004,2003,2001,50</t>
-  </si>
-  <si>
-    <t>8,34,18,2005,2003,2001,50</t>
-  </si>
-  <si>
-    <t>8,35,18,2006,2003,2001,50</t>
-  </si>
-  <si>
-    <t>7,33,18,2004,2003,2001,50</t>
-  </si>
-  <si>
-    <t>7,34,18,2005,2003,2001,50</t>
-  </si>
-  <si>
-    <t>7,35,18,2006,2003,2001,50</t>
-  </si>
-  <si>
-    <t>8,33,18,2004,2003,32,50</t>
-  </si>
-  <si>
-    <t>8,34,18,2005,2003,32,50</t>
-  </si>
-  <si>
-    <t>8,35,18,2006,2003,32,50</t>
-  </si>
-  <si>
-    <t>7,33,18,2004,2003,32,50</t>
-  </si>
-  <si>
-    <t>7,34,18,2005,2003,32,50</t>
-  </si>
-  <si>
-    <t>7,35,18,2006,2003,32,50</t>
-  </si>
-  <si>
-    <t>金色战魂50</t>
-  </si>
-  <si>
-    <t>50,50,50,50,50,50,50</t>
-  </si>
-  <si>
-    <t>金色法魂50</t>
-  </si>
-  <si>
-    <t>金色道魂50</t>
   </si>
 </sst>
 </file>
@@ -1209,10 +1044,11 @@
   <cols>
     <col min="1" max="1" width="6.875" style="3" customWidth="1"/>
     <col min="2" max="2" width="9" style="3"/>
-    <col min="3" max="4" width="9.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14" style="1" customWidth="1"/>
     <col min="5" max="5" width="29.0833333333333" style="1" customWidth="1"/>
     <col min="6" max="6" width="35.25" style="2" customWidth="1"/>
-    <col min="7" max="7" width="12.25" style="2" customWidth="1"/>
+    <col min="7" max="7" width="13.5" style="2" customWidth="1"/>
     <col min="8" max="8" width="13.75" style="3" customWidth="1"/>
     <col min="9" max="16367" width="9" style="3"/>
     <col min="16368" max="16384" width="9" style="2"/>
@@ -1287,7 +1123,7 @@
       <c r="C6" s="2">
         <v>1</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="6" t="s">
         <v>9</v>
       </c>
       <c r="E6" s="7" t="s">
@@ -1304,11 +1140,11 @@
       <c r="C7" s="2">
         <v>2</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>12</v>
+      <c r="D7" s="6" t="s">
+        <v>9</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>11</v>
@@ -1321,11 +1157,11 @@
       <c r="C8" s="2">
         <v>3</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>14</v>
+      <c r="D8" s="6" t="s">
+        <v>9</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>11</v>
@@ -1334,927 +1170,87 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" customHeight="1" spans="1:7">
-      <c r="C9" s="2">
-        <v>4</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" s="2" customFormat="1" customHeight="1" spans="1:7">
-      <c r="C10" s="2">
-        <v>5</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G10" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:7">
-      <c r="C11" s="2">
-        <v>6</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G11" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" s="2" customFormat="1" customHeight="1" spans="1:7">
-      <c r="C12" s="2">
-        <v>7</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G12" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:7">
-      <c r="C13" s="2">
-        <v>8</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G13" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" s="2" customFormat="1" customHeight="1" spans="1:7">
-      <c r="C14" s="2">
-        <v>9</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G14" s="2">
-        <v>3</v>
-      </c>
-    </row>
+    <row r="9" s="2" customFormat="1" customHeight="1"/>
+    <row r="10" s="2" customFormat="1" customHeight="1"/>
+    <row r="11" s="2" customFormat="1" customHeight="1"/>
+    <row r="12" s="2" customFormat="1" customHeight="1"/>
+    <row r="13" s="2" customFormat="1" customHeight="1"/>
+    <row r="14" s="2" customFormat="1" customHeight="1"/>
     <row r="15" s="2" customFormat="1" customHeight="1"/>
-    <row r="16" s="2" customFormat="1" customHeight="1" spans="1:7">
-      <c r="C16" s="2">
-        <v>10</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G16" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C17" s="2">
-        <v>11</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C18" s="2">
-        <v>12</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G18" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C19" s="2">
-        <v>13</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G19" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C20" s="2">
-        <v>14</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G20" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C21" s="2">
-        <v>15</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G21" s="2">
-        <v>3</v>
-      </c>
-    </row>
+    <row r="16" s="2" customFormat="1" customHeight="1"/>
+    <row r="17" s="2" customFormat="1" customHeight="1"/>
+    <row r="18" s="2" customFormat="1" customHeight="1"/>
+    <row r="19" s="2" customFormat="1" customHeight="1"/>
+    <row r="20" s="2" customFormat="1" customHeight="1"/>
+    <row r="21" s="2" customFormat="1" customHeight="1"/>
     <row r="22" s="2" customFormat="1" customHeight="1"/>
-    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C23" s="2">
-        <v>16</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G23" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C24" s="2">
-        <v>17</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G24" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C25" s="2">
-        <v>18</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G25" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C26" s="2">
-        <v>101</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G26" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C27" s="2">
-        <v>102</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G27" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C28" s="2">
-        <v>103</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G28" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C29" s="2">
-        <v>104</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G29" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C30" s="2">
-        <v>105</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F30" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G30" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C31" s="2">
-        <v>106</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G31" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C32" s="2">
-        <v>107</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="F32" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G32" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C33" s="2">
-        <v>108</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G33" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C34" s="2">
-        <v>109</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G34" s="2">
-        <v>3</v>
-      </c>
-    </row>
+    <row r="23" s="2" customFormat="1" customHeight="1"/>
+    <row r="24" s="2" customFormat="1" customHeight="1"/>
+    <row r="25" s="2" customFormat="1" customHeight="1"/>
+    <row r="26" s="2" customFormat="1" customHeight="1"/>
+    <row r="27" s="2" customFormat="1" customHeight="1"/>
+    <row r="28" s="2" customFormat="1" customHeight="1"/>
+    <row r="29" s="2" customFormat="1" customHeight="1"/>
+    <row r="30" s="2" customFormat="1" customHeight="1"/>
+    <row r="31" s="2" customFormat="1" customHeight="1"/>
+    <row r="32" s="2" customFormat="1" customHeight="1"/>
+    <row r="33" s="2" customFormat="1" customHeight="1"/>
+    <row r="34" s="2" customFormat="1" customHeight="1"/>
     <row r="35" s="2" customFormat="1" customHeight="1"/>
-    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C36" s="2">
-        <v>19</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G36" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C37" s="2">
-        <v>20</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G37" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C38" s="2">
-        <v>21</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G38" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C39" s="2">
-        <v>22</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G39" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C40" s="2">
-        <v>23</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G40" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C41" s="2">
-        <v>24</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G41" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C42" s="2">
-        <v>25</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G42" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C43" s="2">
-        <v>26</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G43" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C44" s="2">
-        <v>27</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E44" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="F44" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G44" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C45" s="2">
-        <v>28</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G45" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C46" s="2">
-        <v>29</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="F46" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G46" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="47" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C47" s="2">
-        <v>30</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="F47" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G47" s="2">
-        <v>3</v>
-      </c>
-    </row>
+    <row r="36" s="2" customFormat="1" customHeight="1"/>
+    <row r="37" s="2" customFormat="1" customHeight="1"/>
+    <row r="38" s="2" customFormat="1" customHeight="1"/>
+    <row r="39" s="2" customFormat="1" customHeight="1"/>
+    <row r="40" s="2" customFormat="1" customHeight="1"/>
+    <row r="41" s="2" customFormat="1" customHeight="1"/>
+    <row r="42" s="2" customFormat="1" customHeight="1"/>
+    <row r="43" s="2" customFormat="1" customHeight="1"/>
+    <row r="44" s="2" customFormat="1" customHeight="1"/>
+    <row r="45" s="2" customFormat="1" customHeight="1"/>
+    <row r="46" s="2" customFormat="1" customHeight="1"/>
+    <row r="47" s="2" customFormat="1" customHeight="1"/>
     <row r="48" s="2" customFormat="1" customHeight="1"/>
-    <row r="49" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C49" s="2">
-        <v>31</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E49" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G49" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C50" s="2">
-        <v>32</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E50" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G50" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="51" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C51" s="2">
-        <v>33</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E51" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="F51" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G51" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="52" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C52" s="2">
-        <v>34</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E52" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="F52" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G52" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C53" s="2">
-        <v>35</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="F53" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G53" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="54" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C54" s="2">
-        <v>36</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E54" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="F54" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G54" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C55" s="2">
-        <v>37</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E55" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="F55" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G55" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C56" s="2">
-        <v>38</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E56" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="F56" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G56" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="57" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C57" s="2">
-        <v>39</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E57" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="F57" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G57" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C58" s="2">
-        <v>40</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E58" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="F58" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G58" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C59" s="2">
-        <v>41</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E59" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="F59" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G59" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="60" s="2" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C60" s="2">
-        <v>42</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E60" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="F60" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G60" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" customHeight="1" spans="3:7">
-      <c r="C61" s="2">
-        <v>43</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E61" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F61" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G61" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" customHeight="1" spans="3:7">
-      <c r="C62" s="2">
-        <v>44</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E62" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F62" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G62" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="63" customHeight="1" spans="3:7">
-      <c r="C63" s="2">
-        <v>45</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E63" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="F63" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G63" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="64" customHeight="1" spans="3:7">
-      <c r="C64" s="2">
-        <v>46</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E64" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="F64" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G64" s="2">
-        <v>1</v>
-      </c>
+    <row r="49" s="2" customFormat="1" customHeight="1"/>
+    <row r="50" s="2" customFormat="1" customHeight="1"/>
+    <row r="51" s="2" customFormat="1" customHeight="1"/>
+    <row r="52" s="2" customFormat="1" customHeight="1"/>
+    <row r="53" s="2" customFormat="1" customHeight="1"/>
+    <row r="54" s="2" customFormat="1" customHeight="1"/>
+    <row r="55" s="2" customFormat="1" customHeight="1"/>
+    <row r="56" s="2" customFormat="1" customHeight="1"/>
+    <row r="57" s="2" customFormat="1" customHeight="1"/>
+    <row r="58" s="2" customFormat="1" customHeight="1"/>
+    <row r="59" s="2" customFormat="1" customHeight="1"/>
+    <row r="60" s="2" customFormat="1" customHeight="1"/>
+    <row r="61" customHeight="1" spans="3:5">
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+    </row>
+    <row r="62" customHeight="1" spans="3:5">
+      <c r="C62" s="2"/>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
+    </row>
+    <row r="63" customHeight="1" spans="3:5">
+      <c r="C63" s="2"/>
+      <c r="D63" s="2"/>
+      <c r="E63" s="2"/>
+    </row>
+    <row r="64" customHeight="1" spans="3:5">
+      <c r="C64" s="2"/>
+      <c r="D64" s="2"/>
+      <c r="E64" s="2"/>
     </row>
     <row r="65" customHeight="1" spans="3:7">
-      <c r="C65" s="2">
-        <v>47</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E65" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="F65" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G65" s="2">
-        <v>2</v>
-      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" s="2"/>
+      <c r="E65" s="2"/>
     </row>
     <row r="66" customHeight="1" spans="3:7">
-      <c r="C66" s="2">
-        <v>48</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E66" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="F66" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G66" s="2">
-        <v>3</v>
-      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
     </row>
     <row r="76" customHeight="1" spans="3:7">
       <c r="G76" s="6"/>

--- a/Excel/GiftPackPet.xlsx
+++ b/Excel/GiftPackPet.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="22">
   <si>
     <t>ID</t>
   </si>
@@ -41,6 +41,15 @@
     <t>AttrValueList</t>
   </si>
   <si>
+    <t>TalentList</t>
+  </si>
+  <si>
+    <t>SkillList</t>
+  </si>
+  <si>
+    <t>SkillLevelList</t>
+  </si>
+  <si>
     <t>Role</t>
   </si>
   <si>
@@ -63,6 +72,27 @@
   </si>
   <si>
     <t>40,40,40,40,40</t>
+  </si>
+  <si>
+    <t>10011</t>
+  </si>
+  <si>
+    <t>1002</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>20011</t>
+  </si>
+  <si>
+    <t>2002</t>
+  </si>
+  <si>
+    <t>30011</t>
+  </si>
+  <si>
+    <t>3002</t>
   </si>
 </sst>
 </file>
@@ -1039,8 +1069,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G103"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" outlineLevelCol="6"/>
+  <dimension ref="A1:J103"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="3" customWidth="1"/>
     <col min="2" max="2" width="9" style="3"/>
@@ -1048,21 +1078,23 @@
     <col min="4" max="4" width="14" style="1" customWidth="1"/>
     <col min="5" max="5" width="29.0833333333333" style="1" customWidth="1"/>
     <col min="6" max="6" width="35.25" style="2" customWidth="1"/>
-    <col min="7" max="7" width="13.5" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.75" style="3" customWidth="1"/>
-    <col min="9" max="16367" width="9" style="3"/>
-    <col min="16368" max="16384" width="9" style="2"/>
+    <col min="7" max="7" width="24.5" style="2" customWidth="1"/>
+    <col min="8" max="9" width="20.3333333333333" style="2" customWidth="1"/>
+    <col min="10" max="10" width="13.5" style="2" customWidth="1"/>
+    <col min="11" max="11" width="13.75" style="3" customWidth="1"/>
+    <col min="12" max="16370" width="9" style="3"/>
+    <col min="16371" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:7">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A1" s="3"/>
       <c r="B1" s="3"/>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:7">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:7">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A3" s="3"/>
       <c r="B3" s="4"/>
       <c r="C3" s="5" t="s">
@@ -1080,12 +1112,21 @@
       <c r="G3" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:7">
+      <c r="H3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A4" s="3"/>
       <c r="B4" s="4"/>
       <c r="C4" s="5" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>1</v>
@@ -1099,74 +1140,119 @@
       <c r="G4" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:7">
+      <c r="H4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A5" s="3"/>
       <c r="B5" s="4"/>
       <c r="C5" s="5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="1:7">
+        <v>11</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="C6" s="2">
         <v>1</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" s="2">
+        <v>14</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="1:7">
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="C7" s="2">
         <v>2</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" s="2">
+        <v>14</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" customHeight="1" spans="1:7">
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="C8" s="2">
         <v>3</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" s="2">
+        <v>14</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="2">
         <v>3</v>
       </c>
     </row>
@@ -1242,55 +1328,55 @@
       <c r="D64" s="2"/>
       <c r="E64" s="2"/>
     </row>
-    <row r="65" customHeight="1" spans="3:7">
+    <row r="65" customHeight="1" spans="3:10">
       <c r="C65" s="2"/>
       <c r="D65" s="2"/>
       <c r="E65" s="2"/>
     </row>
-    <row r="66" customHeight="1" spans="3:7">
+    <row r="66" customHeight="1" spans="3:10">
       <c r="C66" s="2"/>
       <c r="D66" s="2"/>
       <c r="E66" s="2"/>
     </row>
-    <row r="76" customHeight="1" spans="3:7">
-      <c r="G76" s="6"/>
-    </row>
-    <row r="77" customHeight="1" spans="3:7">
-      <c r="G77" s="6"/>
-    </row>
-    <row r="78" customHeight="1" spans="3:7">
-      <c r="G78" s="6"/>
-    </row>
-    <row r="79" customHeight="1" spans="3:7">
-      <c r="G79" s="6"/>
-    </row>
-    <row r="80" customHeight="1" spans="3:7">
-      <c r="G80" s="6"/>
-    </row>
-    <row r="81" customHeight="1" spans="7:7">
-      <c r="G81" s="6"/>
-    </row>
-    <row r="82" customHeight="1" spans="7:7">
-      <c r="G82" s="6"/>
-    </row>
-    <row r="83" customHeight="1" spans="7:7">
-      <c r="G83" s="6"/>
-    </row>
-    <row r="84" customHeight="1" spans="7:7">
-      <c r="G84" s="6"/>
-    </row>
-    <row r="101" customHeight="1" spans="7:7">
-      <c r="G101" s="6"/>
-    </row>
-    <row r="102" customHeight="1" spans="7:7">
-      <c r="G102" s="6"/>
-    </row>
-    <row r="103" customHeight="1" spans="7:7">
-      <c r="G103" s="6"/>
+    <row r="76" customHeight="1" spans="3:10">
+      <c r="J76" s="6"/>
+    </row>
+    <row r="77" customHeight="1" spans="3:10">
+      <c r="J77" s="6"/>
+    </row>
+    <row r="78" customHeight="1" spans="3:10">
+      <c r="J78" s="6"/>
+    </row>
+    <row r="79" customHeight="1" spans="3:10">
+      <c r="J79" s="6"/>
+    </row>
+    <row r="80" customHeight="1" spans="3:10">
+      <c r="J80" s="6"/>
+    </row>
+    <row r="81" customHeight="1" spans="10:10">
+      <c r="J81" s="6"/>
+    </row>
+    <row r="82" customHeight="1" spans="10:10">
+      <c r="J82" s="6"/>
+    </row>
+    <row r="83" customHeight="1" spans="10:10">
+      <c r="J83" s="6"/>
+    </row>
+    <row r="84" customHeight="1" spans="10:10">
+      <c r="J84" s="6"/>
+    </row>
+    <row r="101" customHeight="1" spans="10:10">
+      <c r="J101" s="6"/>
+    </row>
+    <row r="102" customHeight="1" spans="10:10">
+      <c r="J102" s="6"/>
+    </row>
+    <row r="103" customHeight="1" spans="10:10">
+      <c r="J103" s="6"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:F5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="I3 I4 I5 C3:H5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/GiftPackPet.xlsx
+++ b/Excel/GiftPackPet.xlsx
@@ -68,10 +68,10 @@
     <t>新手宠物</t>
   </si>
   <si>
-    <t>7,33,18,2004,2003</t>
-  </si>
-  <si>
-    <t>40,40,40,40,40</t>
+    <t>1,2</t>
+  </si>
+  <si>
+    <t>1,10</t>
   </si>
   <si>
     <t>10011</t>
@@ -1376,7 +1376,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="I3 I4 I5 C3:H5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:I5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/GiftPackPet.xlsx
+++ b/Excel/GiftPackPet.xlsx
@@ -27,12 +27,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="23">
   <si>
     <t>ID</t>
   </si>
   <si>
     <t>Name</t>
+  </si>
+  <si>
+    <t>Mid</t>
   </si>
   <si>
     <t>AttrIdList</t>
@@ -1069,32 +1072,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J103"/>
+  <dimension ref="A1:K103"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="3" customWidth="1"/>
     <col min="2" max="2" width="9" style="3"/>
     <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14" style="1" customWidth="1"/>
-    <col min="5" max="5" width="29.0833333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="35.25" style="2" customWidth="1"/>
-    <col min="7" max="7" width="24.5" style="2" customWidth="1"/>
-    <col min="8" max="9" width="20.3333333333333" style="2" customWidth="1"/>
-    <col min="10" max="10" width="13.5" style="2" customWidth="1"/>
-    <col min="11" max="11" width="13.75" style="3" customWidth="1"/>
-    <col min="12" max="16370" width="9" style="3"/>
-    <col min="16371" max="16384" width="9" style="2"/>
+    <col min="4" max="5" width="14" style="1" customWidth="1"/>
+    <col min="6" max="6" width="29.0833333333333" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.25" style="2" customWidth="1"/>
+    <col min="8" max="8" width="24.5" style="2" customWidth="1"/>
+    <col min="9" max="10" width="20.3333333333333" style="2" customWidth="1"/>
+    <col min="11" max="11" width="13.5" style="2" customWidth="1"/>
+    <col min="12" max="12" width="13.75" style="3" customWidth="1"/>
+    <col min="13" max="16371" width="9" style="3"/>
+    <col min="16372" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:10">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A1" s="3"/>
       <c r="B1" s="3"/>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:10">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:10">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A3" s="3"/>
       <c r="B3" s="4"/>
       <c r="C3" s="5" t="s">
@@ -1121,12 +1124,15 @@
       <c r="J3" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K3" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A4" s="3"/>
       <c r="B4" s="4"/>
       <c r="C4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>1</v>
@@ -1149,44 +1155,50 @@
       <c r="J4" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K4" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A5" s="3"/>
       <c r="B5" s="4"/>
       <c r="C5" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>11</v>
-      </c>
       <c r="F5" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="1:10">
+        <v>12</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="1:11">
       <c r="C6" s="2">
         <v>1</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="7" t="s">
         <v>13</v>
+      </c>
+      <c r="E6" s="6">
+        <v>1</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>14</v>
@@ -1200,59 +1212,68 @@
       <c r="I6" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="K6" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="1:10">
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="1:11">
       <c r="C7" s="2">
         <v>2</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="7" t="s">
         <v>13</v>
+      </c>
+      <c r="E7" s="6">
+        <v>1</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>14</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="J7" s="2">
+        <v>20</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="K7" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" customHeight="1" spans="1:10">
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="1:11">
       <c r="C8" s="2">
         <v>3</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="7" t="s">
         <v>13</v>
+      </c>
+      <c r="E8" s="6">
+        <v>1</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>14</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>21</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" s="2">
+        <v>22</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="K8" s="2">
         <v>3</v>
       </c>
     </row>
@@ -1308,75 +1329,81 @@
     <row r="58" s="2" customFormat="1" customHeight="1"/>
     <row r="59" s="2" customFormat="1" customHeight="1"/>
     <row r="60" s="2" customFormat="1" customHeight="1"/>
-    <row r="61" customHeight="1" spans="3:5">
+    <row r="61" customHeight="1" spans="3:6">
       <c r="C61" s="2"/>
       <c r="D61" s="2"/>
       <c r="E61" s="2"/>
-    </row>
-    <row r="62" customHeight="1" spans="3:5">
+      <c r="F61" s="2"/>
+    </row>
+    <row r="62" customHeight="1" spans="3:6">
       <c r="C62" s="2"/>
       <c r="D62" s="2"/>
       <c r="E62" s="2"/>
-    </row>
-    <row r="63" customHeight="1" spans="3:5">
+      <c r="F62" s="2"/>
+    </row>
+    <row r="63" customHeight="1" spans="3:6">
       <c r="C63" s="2"/>
       <c r="D63" s="2"/>
       <c r="E63" s="2"/>
-    </row>
-    <row r="64" customHeight="1" spans="3:5">
+      <c r="F63" s="2"/>
+    </row>
+    <row r="64" customHeight="1" spans="3:6">
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
       <c r="E64" s="2"/>
-    </row>
-    <row r="65" customHeight="1" spans="3:10">
+      <c r="F64" s="2"/>
+    </row>
+    <row r="65" customHeight="1" spans="3:11">
       <c r="C65" s="2"/>
       <c r="D65" s="2"/>
       <c r="E65" s="2"/>
-    </row>
-    <row r="66" customHeight="1" spans="3:10">
+      <c r="F65" s="2"/>
+    </row>
+    <row r="66" customHeight="1" spans="3:11">
       <c r="C66" s="2"/>
       <c r="D66" s="2"/>
       <c r="E66" s="2"/>
-    </row>
-    <row r="76" customHeight="1" spans="3:10">
-      <c r="J76" s="6"/>
-    </row>
-    <row r="77" customHeight="1" spans="3:10">
-      <c r="J77" s="6"/>
-    </row>
-    <row r="78" customHeight="1" spans="3:10">
-      <c r="J78" s="6"/>
-    </row>
-    <row r="79" customHeight="1" spans="3:10">
-      <c r="J79" s="6"/>
-    </row>
-    <row r="80" customHeight="1" spans="3:10">
-      <c r="J80" s="6"/>
-    </row>
-    <row r="81" customHeight="1" spans="10:10">
-      <c r="J81" s="6"/>
-    </row>
-    <row r="82" customHeight="1" spans="10:10">
-      <c r="J82" s="6"/>
-    </row>
-    <row r="83" customHeight="1" spans="10:10">
-      <c r="J83" s="6"/>
-    </row>
-    <row r="84" customHeight="1" spans="10:10">
-      <c r="J84" s="6"/>
-    </row>
-    <row r="101" customHeight="1" spans="10:10">
-      <c r="J101" s="6"/>
-    </row>
-    <row r="102" customHeight="1" spans="10:10">
-      <c r="J102" s="6"/>
-    </row>
-    <row r="103" customHeight="1" spans="10:10">
-      <c r="J103" s="6"/>
+      <c r="F66" s="2"/>
+    </row>
+    <row r="76" customHeight="1" spans="3:11">
+      <c r="K76" s="6"/>
+    </row>
+    <row r="77" customHeight="1" spans="3:11">
+      <c r="K77" s="6"/>
+    </row>
+    <row r="78" customHeight="1" spans="3:11">
+      <c r="K78" s="6"/>
+    </row>
+    <row r="79" customHeight="1" spans="3:11">
+      <c r="K79" s="6"/>
+    </row>
+    <row r="80" customHeight="1" spans="3:11">
+      <c r="K80" s="6"/>
+    </row>
+    <row r="81" customHeight="1" spans="11:11">
+      <c r="K81" s="6"/>
+    </row>
+    <row r="82" customHeight="1" spans="11:11">
+      <c r="K82" s="6"/>
+    </row>
+    <row r="83" customHeight="1" spans="11:11">
+      <c r="K83" s="6"/>
+    </row>
+    <row r="84" customHeight="1" spans="11:11">
+      <c r="K84" s="6"/>
+    </row>
+    <row r="101" customHeight="1" spans="11:11">
+      <c r="K101" s="6"/>
+    </row>
+    <row r="102" customHeight="1" spans="11:11">
+      <c r="K102" s="6"/>
+    </row>
+    <row r="103" customHeight="1" spans="11:11">
+      <c r="K103" s="6"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:I5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 E4 E5 C3:D5 F3:J5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/GiftPackPet.xlsx
+++ b/Excel/GiftPackPet.xlsx
@@ -38,10 +38,10 @@
     <t>Mid</t>
   </si>
   <si>
-    <t>AttrIdList</t>
-  </si>
-  <si>
-    <t>AttrValueList</t>
+    <t>FlairIdList</t>
+  </si>
+  <si>
+    <t>FlairVueList</t>
   </si>
   <si>
     <t>TalentList</t>
@@ -71,31 +71,31 @@
     <t>新手宠物</t>
   </si>
   <si>
-    <t>1,2</t>
-  </si>
-  <si>
-    <t>1,10</t>
+    <t>1,3</t>
+  </si>
+  <si>
+    <t>10,50</t>
   </si>
   <si>
     <t>10011</t>
   </si>
   <si>
-    <t>1002</t>
-  </si>
-  <si>
-    <t>2</t>
+    <t>1002,1004</t>
+  </si>
+  <si>
+    <t>2,2</t>
   </si>
   <si>
     <t>20011</t>
   </si>
   <si>
-    <t>2002</t>
+    <t>2002,2004</t>
   </si>
   <si>
     <t>30011</t>
   </si>
   <si>
-    <t>3002</t>
+    <t>3002,3004</t>
   </si>
 </sst>
 </file>
@@ -1403,7 +1403,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 E4 E5 C3:D5 F3:J5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:J3 C4:E4 F4 G4 H4:J4 C5:J5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/GiftPackPet.xlsx
+++ b/Excel/GiftPackPet.xlsx
@@ -74,10 +74,10 @@
     <t>1,3</t>
   </si>
   <si>
-    <t>10,50</t>
-  </si>
-  <si>
-    <t>10011</t>
+    <t>75,75</t>
+  </si>
+  <si>
+    <t>10022</t>
   </si>
   <si>
     <t>1002,1004</t>
@@ -86,13 +86,13 @@
     <t>2,2</t>
   </si>
   <si>
-    <t>20011</t>
+    <t>20022</t>
   </si>
   <si>
     <t>2002,2004</t>
   </si>
   <si>
-    <t>30011</t>
+    <t>30022</t>
   </si>
   <si>
     <t>3002,3004</t>
@@ -1403,7 +1403,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:J3 C4:E4 F4 G4 H4:J4 C5:J5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:J5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/GiftPackPet.xlsx
+++ b/Excel/GiftPackPet.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\legend2\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="35">
   <si>
     <t>ID</t>
   </si>
@@ -38,6 +43,9 @@
     <t>Mid</t>
   </si>
   <si>
+    <t>TraitId</t>
+  </si>
+  <si>
     <t>FlairIdList</t>
   </si>
   <si>
@@ -56,6 +64,9 @@
     <t>Role</t>
   </si>
   <si>
+    <t>Quality</t>
+  </si>
+  <si>
     <t>Id</t>
   </si>
   <si>
@@ -96,6 +107,36 @@
   </si>
   <si>
     <t>3002,3004</t>
+  </si>
+  <si>
+    <t>多重宠物</t>
+  </si>
+  <si>
+    <t>1,2,3</t>
+  </si>
+  <si>
+    <t>75,75,75</t>
+  </si>
+  <si>
+    <t>10023,10032</t>
+  </si>
+  <si>
+    <t>1002,1003</t>
+  </si>
+  <si>
+    <t>4,4</t>
+  </si>
+  <si>
+    <t>20023,20032</t>
+  </si>
+  <si>
+    <t>2002,2003</t>
+  </si>
+  <si>
+    <t>30023,30033</t>
+  </si>
+  <si>
+    <t>3002,3003</t>
   </si>
 </sst>
 </file>
@@ -1072,32 +1113,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K103"/>
+  <dimension ref="A1:M103"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="3" customWidth="1"/>
     <col min="2" max="2" width="9" style="3"/>
     <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
-    <col min="4" max="5" width="14" style="1" customWidth="1"/>
-    <col min="6" max="6" width="29.0833333333333" style="1" customWidth="1"/>
-    <col min="7" max="7" width="35.25" style="2" customWidth="1"/>
-    <col min="8" max="8" width="24.5" style="2" customWidth="1"/>
-    <col min="9" max="10" width="20.3333333333333" style="2" customWidth="1"/>
-    <col min="11" max="11" width="13.5" style="2" customWidth="1"/>
-    <col min="12" max="12" width="13.75" style="3" customWidth="1"/>
-    <col min="13" max="16371" width="9" style="3"/>
-    <col min="16372" max="16384" width="9" style="2"/>
+    <col min="4" max="6" width="14" style="1" customWidth="1"/>
+    <col min="7" max="7" width="29.0833333333333" style="1" customWidth="1"/>
+    <col min="8" max="8" width="35.25" style="2" customWidth="1"/>
+    <col min="9" max="9" width="24.5" style="2" customWidth="1"/>
+    <col min="10" max="11" width="20.3333333333333" style="2" customWidth="1"/>
+    <col min="12" max="13" width="13.5" style="2" customWidth="1"/>
+    <col min="14" max="16372" width="9" style="3"/>
+    <col min="16373" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:11">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A1" s="3"/>
       <c r="B1" s="3"/>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:11">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:11">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A3" s="3"/>
       <c r="B3" s="4"/>
       <c r="C3" s="5" t="s">
@@ -1127,12 +1167,18 @@
       <c r="K3" s="5" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:11">
+      <c r="L3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A4" s="3"/>
       <c r="B4" s="4"/>
       <c r="C4" s="5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>1</v>
@@ -1158,128 +1204,260 @@
       <c r="K4" s="5" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:11">
+      <c r="L4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A5" s="3"/>
       <c r="B5" s="4"/>
       <c r="C5" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>12</v>
       </c>
       <c r="G5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="M5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="1:11">
+    </row>
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="1:13">
       <c r="C6" s="2">
         <v>1</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E6" s="6">
         <v>1</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>14</v>
+      <c r="F6" s="6">
+        <v>1</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="K6" s="2">
+        <v>19</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="L6" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="1:11">
+      <c r="M6" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="1:13">
       <c r="C7" s="2">
         <v>2</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E7" s="6">
         <v>1</v>
       </c>
-      <c r="F7" s="7" t="s">
-        <v>14</v>
+      <c r="F7" s="6">
+        <v>1</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I7" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="J7" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" s="2" customFormat="1" customHeight="1" spans="1:11">
+      <c r="M7" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="1:13">
       <c r="C8" s="2">
         <v>3</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E8" s="6">
         <v>1</v>
       </c>
-      <c r="F8" s="7" t="s">
-        <v>14</v>
+      <c r="F8" s="6">
+        <v>1</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="K8" s="2">
+        <v>24</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="L8" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" s="2" customFormat="1" customHeight="1"/>
-    <row r="10" s="2" customFormat="1" customHeight="1"/>
-    <row r="11" s="2" customFormat="1" customHeight="1"/>
+      <c r="M8" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="1:13">
+      <c r="C9" s="2">
+        <v>4</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="6">
+        <v>2</v>
+      </c>
+      <c r="F9" s="6">
+        <v>3</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="L9" s="2">
+        <v>1</v>
+      </c>
+      <c r="M9" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="1:13">
+      <c r="C10" s="2">
+        <v>5</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="6">
+        <v>2</v>
+      </c>
+      <c r="F10" s="6">
+        <v>3</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="L10" s="2">
+        <v>2</v>
+      </c>
+      <c r="M10" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:13">
+      <c r="C11" s="2">
+        <v>6</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="6">
+        <v>2</v>
+      </c>
+      <c r="F11" s="6">
+        <v>3</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="L11" s="2">
+        <v>3</v>
+      </c>
+      <c r="M11" s="2">
+        <v>5</v>
+      </c>
+    </row>
     <row r="12" s="2" customFormat="1" customHeight="1"/>
     <row r="13" s="2" customFormat="1" customHeight="1"/>
     <row r="14" s="2" customFormat="1" customHeight="1"/>
@@ -1329,81 +1507,99 @@
     <row r="58" s="2" customFormat="1" customHeight="1"/>
     <row r="59" s="2" customFormat="1" customHeight="1"/>
     <row r="60" s="2" customFormat="1" customHeight="1"/>
-    <row r="61" customHeight="1" spans="3:6">
+    <row r="61" customHeight="1" spans="3:7">
       <c r="C61" s="2"/>
       <c r="D61" s="2"/>
       <c r="E61" s="2"/>
       <c r="F61" s="2"/>
-    </row>
-    <row r="62" customHeight="1" spans="3:6">
+      <c r="G61" s="2"/>
+    </row>
+    <row r="62" customHeight="1" spans="3:7">
       <c r="C62" s="2"/>
       <c r="D62" s="2"/>
       <c r="E62" s="2"/>
       <c r="F62" s="2"/>
-    </row>
-    <row r="63" customHeight="1" spans="3:6">
+      <c r="G62" s="2"/>
+    </row>
+    <row r="63" customHeight="1" spans="3:7">
       <c r="C63" s="2"/>
       <c r="D63" s="2"/>
       <c r="E63" s="2"/>
       <c r="F63" s="2"/>
-    </row>
-    <row r="64" customHeight="1" spans="3:6">
+      <c r="G63" s="2"/>
+    </row>
+    <row r="64" customHeight="1" spans="3:7">
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
       <c r="E64" s="2"/>
       <c r="F64" s="2"/>
-    </row>
-    <row r="65" customHeight="1" spans="3:11">
+      <c r="G64" s="2"/>
+    </row>
+    <row r="65" customHeight="1" spans="3:13">
       <c r="C65" s="2"/>
       <c r="D65" s="2"/>
       <c r="E65" s="2"/>
       <c r="F65" s="2"/>
-    </row>
-    <row r="66" customHeight="1" spans="3:11">
+      <c r="G65" s="2"/>
+    </row>
+    <row r="66" customHeight="1" spans="3:13">
       <c r="C66" s="2"/>
       <c r="D66" s="2"/>
       <c r="E66" s="2"/>
       <c r="F66" s="2"/>
-    </row>
-    <row r="76" customHeight="1" spans="3:11">
-      <c r="K76" s="6"/>
-    </row>
-    <row r="77" customHeight="1" spans="3:11">
-      <c r="K77" s="6"/>
-    </row>
-    <row r="78" customHeight="1" spans="3:11">
-      <c r="K78" s="6"/>
-    </row>
-    <row r="79" customHeight="1" spans="3:11">
-      <c r="K79" s="6"/>
-    </row>
-    <row r="80" customHeight="1" spans="3:11">
-      <c r="K80" s="6"/>
-    </row>
-    <row r="81" customHeight="1" spans="11:11">
-      <c r="K81" s="6"/>
-    </row>
-    <row r="82" customHeight="1" spans="11:11">
-      <c r="K82" s="6"/>
-    </row>
-    <row r="83" customHeight="1" spans="11:11">
-      <c r="K83" s="6"/>
-    </row>
-    <row r="84" customHeight="1" spans="11:11">
-      <c r="K84" s="6"/>
-    </row>
-    <row r="101" customHeight="1" spans="11:11">
-      <c r="K101" s="6"/>
-    </row>
-    <row r="102" customHeight="1" spans="11:11">
-      <c r="K102" s="6"/>
-    </row>
-    <row r="103" customHeight="1" spans="11:11">
-      <c r="K103" s="6"/>
+      <c r="G66" s="2"/>
+    </row>
+    <row r="76" customHeight="1" spans="3:13">
+      <c r="L76" s="6"/>
+      <c r="M76" s="6"/>
+    </row>
+    <row r="77" customHeight="1" spans="3:13">
+      <c r="L77" s="6"/>
+      <c r="M77" s="6"/>
+    </row>
+    <row r="78" customHeight="1" spans="3:13">
+      <c r="L78" s="6"/>
+      <c r="M78" s="6"/>
+    </row>
+    <row r="79" customHeight="1" spans="3:13">
+      <c r="L79" s="6"/>
+      <c r="M79" s="6"/>
+    </row>
+    <row r="80" customHeight="1" spans="3:13">
+      <c r="L80" s="6"/>
+      <c r="M80" s="6"/>
+    </row>
+    <row r="81" customHeight="1" spans="12:13">
+      <c r="L81" s="6"/>
+      <c r="M81" s="6"/>
+    </row>
+    <row r="82" customHeight="1" spans="12:13">
+      <c r="L82" s="6"/>
+      <c r="M82" s="6"/>
+    </row>
+    <row r="83" customHeight="1" spans="12:13">
+      <c r="L83" s="6"/>
+      <c r="M83" s="6"/>
+    </row>
+    <row r="84" customHeight="1" spans="12:13">
+      <c r="L84" s="6"/>
+      <c r="M84" s="6"/>
+    </row>
+    <row r="101" customHeight="1" spans="12:13">
+      <c r="L101" s="6"/>
+      <c r="M101" s="6"/>
+    </row>
+    <row r="102" customHeight="1" spans="12:13">
+      <c r="L102" s="6"/>
+      <c r="M102" s="6"/>
+    </row>
+    <row r="103" customHeight="1" spans="12:13">
+      <c r="L103" s="6"/>
+      <c r="M103" s="6"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:J5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="F3 F4 F5 C3:E5 G3:K5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/GiftPackPet.xlsx
+++ b/Excel/GiftPackPet.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="39">
   <si>
     <t>ID</t>
   </si>
@@ -137,6 +137,18 @@
   </si>
   <si>
     <t>3002,3003</t>
+  </si>
+  <si>
+    <t>双减宠物</t>
+  </si>
+  <si>
+    <t>10021,10024</t>
+  </si>
+  <si>
+    <t>20021,20024</t>
+  </si>
+  <si>
+    <t>30021,30024</t>
   </si>
 </sst>
 </file>
@@ -1458,9 +1470,111 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" s="2" customFormat="1" customHeight="1"/>
-    <row r="13" s="2" customFormat="1" customHeight="1"/>
-    <row r="14" s="2" customFormat="1" customHeight="1"/>
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="1:13">
+      <c r="C12" s="2">
+        <v>7</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="6">
+        <v>3</v>
+      </c>
+      <c r="F12" s="6">
+        <v>3</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="L12" s="2">
+        <v>1</v>
+      </c>
+      <c r="M12" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:13">
+      <c r="C13" s="2">
+        <v>8</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="6">
+        <v>3</v>
+      </c>
+      <c r="F13" s="6">
+        <v>3</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="L13" s="2">
+        <v>2</v>
+      </c>
+      <c r="M13" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="1:13">
+      <c r="C14" s="2">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" s="6">
+        <v>3</v>
+      </c>
+      <c r="F14" s="6">
+        <v>3</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="L14" s="2">
+        <v>3</v>
+      </c>
+      <c r="M14" s="2">
+        <v>5</v>
+      </c>
+    </row>
     <row r="15" s="2" customFormat="1" customHeight="1"/>
     <row r="16" s="2" customFormat="1" customHeight="1"/>
     <row r="17" s="2" customFormat="1" customHeight="1"/>
@@ -1599,7 +1713,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="F3 F4 F5 C3:E5 G3:K5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:K5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
